--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\7sher\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863A5F3C-6834-467C-A2BD-0599A31CFF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2B5FDC-A0AB-4AFC-81DD-8DB469EACC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="1140" windowWidth="16245" windowHeight="13245" activeTab="1" xr2:uid="{B5255683-9904-4B96-B116-504FB2085B5B}"/>
+    <workbookView xWindow="2025" yWindow="570" windowWidth="18030" windowHeight="13680" activeTab="2" xr2:uid="{B5255683-9904-4B96-B116-504FB2085B5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Model" sheetId="2" r:id="rId2"/>
     <sheet name="CC Model" sheetId="4" r:id="rId3"/>
     <sheet name="Literature" sheetId="3" r:id="rId4"/>
+    <sheet name="Management" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -183,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="191">
   <si>
     <t>Price</t>
   </si>
@@ -632,9 +633,6 @@
     <t>Takeaways:</t>
   </si>
   <si>
-    <t>If NonENT  ARPU avg is less than ~12 then ADBE isnt worth much as a lot more ENT revenue is at risk</t>
-  </si>
-  <si>
     <t>If NonENT ARPU avg is &gt;=20 ADBE is worth a lot more</t>
   </si>
   <si>
@@ -666,6 +664,99 @@
   </si>
   <si>
     <t>Random Notes:</t>
+  </si>
+  <si>
+    <t>Current CEO takes over, was COO since 2005</t>
+  </si>
+  <si>
+    <t>Adobe stagnates as its business model is outdated and not innovating</t>
+  </si>
+  <si>
+    <t>Adobe transitions to a monthly subscription model and starts focusing on enterprise deals and software</t>
+  </si>
+  <si>
+    <t>Post 2014</t>
+  </si>
+  <si>
+    <t>The new direction of the company which marks the current model of Adobe is very successful</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Current Opinion:</t>
+  </si>
+  <si>
+    <t>Adobe is slightly undervalued with very conservative values. A lot of turn around potential with great management.</t>
+  </si>
+  <si>
+    <t>Adobe's future is highly dependent on the mangement's execution and if Jevon's Paradox will accelerate growth after seat diminishment</t>
+  </si>
+  <si>
+    <t>Firefly: Adobe's AI Suite</t>
+  </si>
+  <si>
+    <t>Creative Cloud: Digital Art, Visual Media, Digital Editing, etc. Suite of tools package</t>
+  </si>
+  <si>
+    <t>AEP, AEM: Adobe's Enterprise Software</t>
+  </si>
+  <si>
+    <t>Firefly trained on images Adobe had the legal right to train on; Most AI models are trained on data skimmed from the internet</t>
+  </si>
+  <si>
+    <t>The key drivers are: Enterprise Firefly adoption, AI generated content legality, Jevon's Paradox increasing industry adoption of tools, and Firefly/Adobe's GenAI ability to raise ARPU through increased use of gen tokens.</t>
+  </si>
+  <si>
+    <t>Acrobat: Industry Standard Document Tool</t>
+  </si>
+  <si>
+    <t>Explainations of The Main Assumptions:</t>
+  </si>
+  <si>
+    <t>CC Enterprise Revenue drops 50% due to 50% seat reduction from a 100% increase in productivity from AI tools.</t>
+  </si>
+  <si>
+    <t>CC Non-Enterprise Revenue &amp; ARPU is basically unchanged due to the elasticity of Digital Art/Visual Media jobs in non-corporate settings. This assumption is very conservative as GenAI and producitvity could lead to a lot higher adoption rate.</t>
+  </si>
+  <si>
+    <t>AEP, AEM Revenue drops 25% to be conservative for less enterprise software seats even though more generated content could provide somewhat of a protection for these contracts.</t>
+  </si>
+  <si>
+    <t>Acrobat Revenue grows at a normal rate, industry standard tool not likely to be changed.</t>
+  </si>
+  <si>
+    <t>CC Enterprise and Non-Enterprise was reconstructed through some logic explained in the CC Model and sensitivity tested where the max limit in both directions would only result in a &lt;30% difference in calculated share price</t>
+  </si>
+  <si>
+    <t>CC Enterprise ARPU grows 65% due to GenAI tokens and its ability to replace employees. This could be a key driver if GenAI legality becomes more questionable. 65% is also very conservative if you take into account that I am modeling this tool replaceing half of workers, Adobe could easily justify 200% or more depending on execution and market dynamics. This is also not sensitive at all and only really changes the share price drastically at a very large increase in ARPU.</t>
+  </si>
+  <si>
+    <t>Base Case: Firefly gets some adoption in enterprise clients and enterprise seats get drastically cut. The stock remains relatively unchanged around 300</t>
+  </si>
+  <si>
+    <t>Bull Case: Adobe's management executes Firefly well and GenAI legality increases Firefly adoption among enterprise clients and allows them to drastically raise ARPU through the cost savings of increased productivity and less seats and Jevon's Paradox helps regain some seats. Depending on market dynamics it could raise the price anywhere from the high 300s to the previous highs in the best circumstances.</t>
+  </si>
+  <si>
+    <t>Bear Case: Jevon's Paradox never kicks in, enterprise clients don’t adopt firefly, and even non enterprise seats are cut. Drop to around the low 200s</t>
+  </si>
+  <si>
+    <t>ARPU Sensitivity Analysis</t>
+  </si>
+  <si>
+    <t>Firefly?</t>
+  </si>
+  <si>
+    <t>Adobe GenAI seat reduction fears stock collapses ~40%</t>
+  </si>
+  <si>
+    <t>If NonENT  ARPU avg is &lt;= 10 then ADBE isnt worth much as a lot more ENT revenue is at risk</t>
+  </si>
+  <si>
+    <t>ENT ARPU</t>
+  </si>
+  <si>
+    <t>Percent Change In Share Price NPV as Discount Rate and Enterprise ARPU Exit Rate Change</t>
   </si>
 </sst>
 </file>
@@ -834,7 +925,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -855,7 +946,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1375,10 +1465,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B5A162-EAE9-4CC5-AE4B-8B686CFC5399}">
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="3" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
@@ -1393,12 +1484,15 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="26"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="33" t="s">
+        <v>169</v>
+      </c>
       <c r="F3" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>1</v>
@@ -1406,16 +1500,19 @@
       <c r="K3" s="4">
         <v>410.5</v>
       </c>
-      <c r="L3" s="25" t="s">
+      <c r="L3" s="24" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="33" t="s">
+        <v>170</v>
+      </c>
       <c r="F4" s="12" t="s">
         <v>75</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>2</v>
@@ -1424,14 +1521,17 @@
         <f>K3*K2</f>
         <v>107551</v>
       </c>
-      <c r="L4" s="25"/>
+      <c r="L4" s="24"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F5" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>157</v>
+      <c r="B5" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>156</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>3</v>
@@ -1440,16 +1540,19 @@
         <f>5431+1164</f>
         <v>6595</v>
       </c>
-      <c r="L5" s="25" t="s">
+      <c r="L5" s="24" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F6" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>158</v>
+      <c r="B6" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="F6" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>157</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>4</v>
@@ -1458,7 +1561,7 @@
         <f>6210+469+125+361+508</f>
         <v>7673</v>
       </c>
-      <c r="L6" s="25" t="s">
+      <c r="L6" s="24" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1467,7 +1570,7 @@
         <v>76</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>5</v>
@@ -1482,7 +1585,7 @@
         <v>79</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K8" s="3" t="e">
         <f>K2/(1.1*4*Model!G47)</f>
@@ -1490,205 +1593,271 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J9" s="17" t="s">
+      <c r="J9" s="33" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="25"/>
+      <c r="F11" s="33" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F12" s="33" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F13" s="33" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F15" s="33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F16" s="33" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F17" s="33" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F18" s="33" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F19" s="33" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F20" s="33" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F21" s="33" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F22" s="33"/>
+    </row>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F23" s="33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F24" s="33" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="25" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F25" s="33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="26" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F26" s="33"/>
+    </row>
+    <row r="27" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F27" s="33" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F28" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="J10" s="17"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="26"/>
-      <c r="F11" s="26" t="s">
+    </row>
+    <row r="29" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F29" s="25" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F13" s="23" t="s">
+    <row r="30" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F30" s="33" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F32" s="22" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F14" s="23" t="s">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F33" s="22" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F15" s="23" t="s">
+    <row r="34" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F34" s="22" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F16" s="23" t="s">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F35" s="22" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F17" s="23"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F18" s="34" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F19" s="31" t="s">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F36" s="22"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F37" s="33" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F38" s="30" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F20" s="31" t="s">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F39" s="30" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F21" s="31" t="s">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F40" s="30" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F22" s="31" t="s">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F41" s="30" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F23" s="31" t="s">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B42" s="25"/>
+      <c r="F42" s="30" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F24" s="23"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F25" s="23"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F26" s="23"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F27" s="23"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F28" s="23"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F30" s="29"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B32" s="26"/>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B33" s="26"/>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C34" s="26"/>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C35" s="26"/>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C36" s="26"/>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B37" s="26"/>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C38" s="26"/>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C39" s="26"/>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C41" s="29"/>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C42" s="29"/>
-      <c r="E42" s="27"/>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C43" s="29"/>
-      <c r="E43" s="27"/>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C44" s="28"/>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C45" s="28"/>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B46" s="29"/>
-      <c r="C46" s="28"/>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C47" s="28"/>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C48" s="29"/>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B43" s="25"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C44" s="25"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C45" s="25"/>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C46" s="25"/>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B47" s="25"/>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C48" s="25"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C49" s="29"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
+      <c r="C49" s="25"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
+      <c r="C51" s="28"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
+      <c r="C52" s="28"/>
+      <c r="E52" s="26"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C53" s="29"/>
-      <c r="D53" s="29"/>
+      <c r="C53" s="28"/>
+      <c r="E53" s="26"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C54" s="29"/>
+      <c r="C54" s="27"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C55" s="29"/>
+      <c r="C55" s="27"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C56" s="29"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="27"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C57" s="29"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="28"/>
+      <c r="C57" s="27"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C58" s="29"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="29"/>
+      <c r="C58" s="28"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C59" s="29"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="29"/>
+      <c r="C59" s="28"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C60" s="29"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="29"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C61" s="29"/>
-      <c r="D61" s="4"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C62" s="29"/>
+      <c r="A62" s="28"/>
+      <c r="C62" s="28"/>
+      <c r="D62" s="28"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C63" s="29"/>
+      <c r="C63" s="28"/>
+      <c r="D63" s="28"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C64" s="29"/>
+      <c r="C64" s="28"/>
+    </row>
+    <row r="65" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C65" s="28"/>
+    </row>
+    <row r="66" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C66" s="28"/>
+    </row>
+    <row r="67" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C67" s="28"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="27"/>
+    </row>
+    <row r="68" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C68" s="28"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="28"/>
+    </row>
+    <row r="69" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C69" s="28"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="28"/>
+    </row>
+    <row r="70" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C70" s="28"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="28"/>
+    </row>
+    <row r="71" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C71" s="28"/>
+      <c r="D71" s="4"/>
+    </row>
+    <row r="72" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C72" s="28"/>
+    </row>
+    <row r="73" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C73" s="28"/>
+    </row>
+    <row r="74" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C74" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1697,7 +1866,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1F5702-5366-4A93-A101-38C235480BE9}">
-  <dimension ref="A1:EA124"/>
+  <dimension ref="A1:EA127"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="6" customWidth="1"/>
@@ -1708,7 +1877,9 @@
     <col min="9" max="18" width="9.140625" style="7"/>
     <col min="19" max="24" width="9.140625" style="6"/>
     <col min="25" max="25" width="9.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="6"/>
+    <col min="26" max="32" width="9.140625" style="6"/>
+    <col min="33" max="33" width="10.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.2">
@@ -1814,7 +1985,7 @@
         <f t="shared" ref="AD2" si="2">AC2+1</f>
         <v>2030</v>
       </c>
-      <c r="AE2" s="35" t="s">
+      <c r="AE2" s="34" t="s">
         <v>122</v>
       </c>
       <c r="AF2" s="8"/>
@@ -1822,7 +1993,7 @@
       <c r="AH2" s="8"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>71</v>
       </c>
       <c r="S3" s="8"/>
@@ -1844,7 +2015,7 @@
       <c r="AH3" s="8"/>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>70</v>
       </c>
       <c r="S4" s="8"/>
@@ -1869,7 +2040,7 @@
       <c r="AH4" s="8"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="27" t="s">
         <v>69</v>
       </c>
       <c r="S5" s="8"/>
@@ -1911,7 +2082,7 @@
       <c r="AH6" s="8"/>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="32" t="s">
         <v>113</v>
       </c>
       <c r="S7" s="8"/>
@@ -1948,7 +2119,7 @@
       <c r="AH7" s="8"/>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="32" t="s">
         <v>112</v>
       </c>
       <c r="S8" s="8"/>
@@ -1986,7 +2157,7 @@
       <c r="AH8" s="8"/>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="32" t="s">
         <v>115</v>
       </c>
       <c r="S9" s="8"/>
@@ -2024,7 +2195,7 @@
       <c r="AH9" s="8"/>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="32" t="s">
         <v>114</v>
       </c>
       <c r="S10" s="8"/>
@@ -2057,7 +2228,7 @@
       <c r="AH10" s="8"/>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="32" t="s">
         <v>110</v>
       </c>
       <c r="S11" s="8"/>
@@ -2078,15 +2249,15 @@
         <f>Z11*0.5</f>
         <v>3.6289999999999996</v>
       </c>
-      <c r="AB11" s="35">
+      <c r="AB11" s="34">
         <f>AA11*1.14</f>
         <v>4.1370599999999991</v>
       </c>
-      <c r="AC11" s="35">
+      <c r="AC11" s="34">
         <f t="shared" ref="AC11:AD11" si="6">AB11*1.14</f>
         <v>4.7162483999999987</v>
       </c>
-      <c r="AD11" s="35">
+      <c r="AD11" s="34">
         <f t="shared" si="6"/>
         <v>5.3765231759999983</v>
       </c>
@@ -2095,7 +2266,7 @@
       <c r="AH11" s="8"/>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="32" t="s">
         <v>111</v>
       </c>
       <c r="S12" s="8"/>
@@ -2115,12 +2286,15 @@
         <v>100</v>
       </c>
       <c r="AB12" s="8">
+        <f>AA12</f>
         <v>100</v>
       </c>
       <c r="AC12" s="8">
+        <f t="shared" ref="AC12:AD12" si="7">AB12</f>
         <v>100</v>
       </c>
       <c r="AD12" s="8">
+        <f t="shared" si="7"/>
         <v>100</v>
       </c>
       <c r="AE12" s="8"/>
@@ -2128,7 +2302,7 @@
       <c r="AH12" s="8"/>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="32" t="s">
         <v>119</v>
       </c>
       <c r="S13" s="8"/>
@@ -2147,7 +2321,7 @@
       <c r="AH13" s="8"/>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="32" t="s">
         <v>118</v>
       </c>
       <c r="S14" s="8"/>
@@ -2156,7 +2330,7 @@
       <c r="V14" s="8"/>
       <c r="W14" s="8"/>
       <c r="X14" s="8"/>
-      <c r="Y14" s="37"/>
+      <c r="Y14" s="36"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="12"/>
       <c r="AC14" s="8"/>
@@ -2202,45 +2376,45 @@
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="30"/>
-      <c r="X16" s="30">
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+      <c r="W16" s="29"/>
+      <c r="X16" s="29">
         <v>5370</v>
       </c>
-      <c r="Y16" s="30">
+      <c r="Y16" s="29">
         <f>Y26</f>
         <v>5850</v>
       </c>
-      <c r="Z16" s="30">
+      <c r="Z16" s="29">
         <f>Y16*1.09</f>
         <v>6376.5000000000009</v>
       </c>
-      <c r="AA16" s="30">
+      <c r="AA16" s="29">
         <f>Z16*0.75</f>
         <v>4782.3750000000009</v>
       </c>
-      <c r="AB16" s="30">
-        <f t="shared" ref="AB16:AD16" si="7">AA16*1.09</f>
+      <c r="AB16" s="29">
+        <f t="shared" ref="AB16:AD16" si="8">AA16*1.09</f>
         <v>5212.7887500000015</v>
       </c>
-      <c r="AC16" s="30">
-        <f t="shared" si="7"/>
+      <c r="AC16" s="29">
+        <f t="shared" si="8"/>
         <v>5681.9397375000017</v>
       </c>
-      <c r="AD16" s="30">
-        <f t="shared" si="7"/>
+      <c r="AD16" s="29">
+        <f t="shared" si="8"/>
         <v>6193.314313875002</v>
       </c>
-      <c r="AE16" s="30"/>
-      <c r="AF16" s="30"/>
-      <c r="AG16" s="30"/>
-      <c r="AH16" s="30"/>
+      <c r="AE16" s="29"/>
+      <c r="AF16" s="29"/>
+      <c r="AG16" s="29"/>
+      <c r="AH16" s="29"/>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="27" t="s">
         <v>73</v>
       </c>
       <c r="S17" s="8"/>
@@ -2252,10 +2426,10 @@
         <v>12680</v>
       </c>
       <c r="Y17" s="8">
-        <f t="shared" ref="Y17:Z21" si="8">X17*1.1</f>
+        <f t="shared" ref="Y17:Z21" si="9">X17*1.1</f>
         <v>13948.000000000002</v>
       </c>
-      <c r="Z17" s="32"/>
+      <c r="Z17" s="31"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
       <c r="AC17" s="8"/>
@@ -2295,73 +2469,73 @@
         <v>3523.5200000000013</v>
       </c>
       <c r="P18" s="10">
-        <f t="shared" ref="P18:X18" si="9">O18*1.12</f>
+        <f t="shared" ref="P18:X18" si="10">O18*1.12</f>
         <v>3946.3424000000018</v>
       </c>
       <c r="Q18" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4419.9034880000027</v>
       </c>
       <c r="R18" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4950.2919065600036</v>
       </c>
       <c r="S18" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5544.3269353472042</v>
       </c>
       <c r="T18" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6209.6461675888695</v>
       </c>
       <c r="U18" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6954.8037076995342</v>
       </c>
       <c r="V18" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7789.3801526234793</v>
       </c>
       <c r="W18" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8724.1057709382967</v>
       </c>
       <c r="X18" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9770.9984634508928</v>
       </c>
-      <c r="Y18" s="30">
+      <c r="Y18" s="29">
         <f>Y17-Y22</f>
         <v>10638.000000000002</v>
       </c>
-      <c r="Z18" s="30">
+      <c r="Z18" s="29">
         <f>SUM(Z19:Z20)</f>
         <v>11824.619999999999</v>
       </c>
-      <c r="AA18" s="30">
+      <c r="AA18" s="29">
         <f>SUM(AA19:AA20)</f>
         <v>12027.074559999999</v>
       </c>
-      <c r="AB18" s="30">
-        <f t="shared" ref="AB18:AD18" si="10">SUM(AB19:AB20)</f>
+      <c r="AB18" s="29">
+        <f t="shared" ref="AB18:AD18" si="11">SUM(AB19:AB20)</f>
         <v>13327.2512704</v>
       </c>
-      <c r="AC18" s="30">
-        <f t="shared" si="10"/>
+      <c r="AC18" s="29">
+        <f t="shared" si="11"/>
         <v>14774.927484735999</v>
       </c>
-      <c r="AD18" s="30">
-        <f t="shared" si="10"/>
+      <c r="AD18" s="29">
+        <f t="shared" si="11"/>
         <v>16387.645862362238</v>
       </c>
-      <c r="AE18" s="30"/>
-      <c r="AF18" s="30"/>
-      <c r="AG18" s="30"/>
-      <c r="AH18" s="30"/>
+      <c r="AE18" s="29"/>
+      <c r="AF18" s="29"/>
+      <c r="AG18" s="29"/>
+      <c r="AH18" s="29"/>
     </row>
     <row r="19" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="32" t="s">
         <v>88</v>
       </c>
       <c r="C19" s="1"/>
@@ -2372,38 +2546,38 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="Y19" s="35">
+      <c r="Y19" s="34">
         <f>Y12*12*Y11</f>
         <v>4584</v>
       </c>
-      <c r="Z19" s="35">
-        <f t="shared" ref="Z19" si="11">Y19*1.14</f>
+      <c r="Z19" s="34">
+        <f t="shared" ref="Z19" si="12">Y19*1.14</f>
         <v>5225.7599999999993</v>
       </c>
-      <c r="AA19" s="35">
+      <c r="AA19" s="34">
         <f>AA12*12*AA11</f>
         <v>4354.7999999999993</v>
       </c>
-      <c r="AB19" s="35">
-        <f t="shared" ref="AB19:AD19" si="12">AB12*12*AB11</f>
+      <c r="AB19" s="34">
+        <f t="shared" ref="AB19:AD19" si="13">AB12*12*AB11</f>
         <v>4964.4719999999988</v>
       </c>
-      <c r="AC19" s="35">
-        <f t="shared" si="12"/>
+      <c r="AC19" s="34">
+        <f t="shared" si="13"/>
         <v>5659.4980799999985</v>
       </c>
-      <c r="AD19" s="35">
-        <f t="shared" si="12"/>
+      <c r="AD19" s="34">
+        <f t="shared" si="13"/>
         <v>6451.827811199998</v>
       </c>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="30"/>
-      <c r="AG19" s="30"/>
-      <c r="AH19" s="30"/>
+      <c r="AE19" s="29"/>
+      <c r="AF19" s="29"/>
+      <c r="AG19" s="29"/>
+      <c r="AH19" s="29"/>
     </row>
     <row r="20" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="32" t="s">
         <v>85</v>
       </c>
       <c r="C20" s="1"/>
@@ -2414,50 +2588,50 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="33"/>
-      <c r="U20" s="33"/>
-      <c r="V20" s="33"/>
-      <c r="W20" s="33"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="35">
+      <c r="L20" s="33"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="34">
         <f>Y10*12*Y9</f>
         <v>6054</v>
       </c>
-      <c r="Z20" s="35">
+      <c r="Z20" s="34">
         <f>Y20*1.09</f>
         <v>6598.8600000000006</v>
       </c>
-      <c r="AA20" s="35">
+      <c r="AA20" s="34">
         <f>AA10*12*AA9</f>
         <v>7672.2745599999998</v>
       </c>
-      <c r="AB20" s="35">
-        <f t="shared" ref="AB20:AD20" si="13">AB10*12*AB9</f>
+      <c r="AB20" s="34">
+        <f t="shared" ref="AB20:AD20" si="14">AB10*12*AB9</f>
         <v>8362.7792704000003</v>
       </c>
-      <c r="AC20" s="35">
-        <f t="shared" si="13"/>
+      <c r="AC20" s="34">
+        <f t="shared" si="14"/>
         <v>9115.4294047360017</v>
       </c>
-      <c r="AD20" s="35">
-        <f t="shared" si="13"/>
+      <c r="AD20" s="34">
+        <f t="shared" si="14"/>
         <v>9935.8180511622413</v>
       </c>
-      <c r="AE20" s="30"/>
-      <c r="AF20" s="30"/>
-      <c r="AG20" s="30"/>
-      <c r="AH20" s="30"/>
+      <c r="AE20" s="29"/>
+      <c r="AF20" s="29"/>
+      <c r="AG20" s="29"/>
+      <c r="AH20" s="29"/>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="27" t="s">
         <v>74</v>
       </c>
       <c r="S21" s="8"/>
@@ -2469,11 +2643,11 @@
         <v>3180</v>
       </c>
       <c r="Y21" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3498.0000000000005</v>
       </c>
       <c r="Z21" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3847.8000000000006</v>
       </c>
       <c r="AA21" s="8"/>
@@ -2486,7 +2660,7 @@
       <c r="AH21" s="8"/>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="27" t="s">
         <v>77</v>
       </c>
       <c r="S22" s="8"/>
@@ -2534,40 +2708,40 @@
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30">
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="29">
         <f>SUM(Y21:Y22)</f>
         <v>6808</v>
       </c>
-      <c r="Z23" s="30">
+      <c r="Z23" s="29">
         <f>SUM(Z21:Z22)</f>
         <v>7488.8000000000011</v>
       </c>
-      <c r="AA23" s="30">
+      <c r="AA23" s="29">
         <f>Z23*1.1</f>
         <v>8237.6800000000021</v>
       </c>
-      <c r="AB23" s="30">
-        <f t="shared" ref="AB23:AD23" si="14">AA23*1.1</f>
+      <c r="AB23" s="29">
+        <f t="shared" ref="AB23:AD23" si="15">AA23*1.1</f>
         <v>9061.448000000004</v>
       </c>
-      <c r="AC23" s="30">
-        <f t="shared" si="14"/>
+      <c r="AC23" s="29">
+        <f t="shared" si="15"/>
         <v>9967.5928000000058</v>
       </c>
-      <c r="AD23" s="30">
-        <f t="shared" si="14"/>
+      <c r="AD23" s="29">
+        <f t="shared" si="15"/>
         <v>10964.352080000008</v>
       </c>
-      <c r="AE23" s="30"/>
-      <c r="AF23" s="30"/>
-      <c r="AG23" s="30"/>
-      <c r="AH23" s="30"/>
+      <c r="AE23" s="29"/>
+      <c r="AF23" s="29"/>
+      <c r="AG23" s="29"/>
+      <c r="AH23" s="29"/>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.2">
       <c r="S24" s="8"/>
@@ -2617,7 +2791,7 @@
       <c r="T25" s="8">
         <v>9230</v>
       </c>
-      <c r="U25" s="35">
+      <c r="U25" s="34">
         <f>T25*1.15</f>
         <v>10614.5</v>
       </c>
@@ -2871,11 +3045,11 @@
         <v>17606</v>
       </c>
       <c r="W31" s="10">
-        <f t="shared" ref="W31:X31" si="15">SUM(W28:W30)</f>
+        <f t="shared" ref="W31:X31" si="16">SUM(W28:W30)</f>
         <v>19409</v>
       </c>
       <c r="X31" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>21505</v>
       </c>
       <c r="Y31" s="10">
@@ -2886,19 +3060,19 @@
         <v>25689.919999999998</v>
       </c>
       <c r="AA31" s="10">
-        <f t="shared" ref="AA31:AD31" si="16">AA23+AA18+AA16</f>
+        <f t="shared" ref="AA31:AD31" si="17">AA23+AA18+AA16</f>
         <v>25047.129560000001</v>
       </c>
       <c r="AB31" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>27601.488020400007</v>
       </c>
       <c r="AC31" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>30424.460022236006</v>
       </c>
       <c r="AD31" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>33545.312256237245</v>
       </c>
       <c r="AE31" s="10">
@@ -2983,19 +3157,19 @@
         <v>598</v>
       </c>
       <c r="E35" s="7">
-        <f t="shared" ref="E35:H35" si="17">SUM(E32:E34)</f>
+        <f t="shared" ref="E35:H35" si="18">SUM(E32:E34)</f>
         <v>0</v>
       </c>
       <c r="F35" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G35" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H35" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>638</v>
       </c>
       <c r="I35" s="6">
@@ -3031,35 +3205,35 @@
         <v>2165</v>
       </c>
       <c r="W35" s="6">
-        <f t="shared" ref="W35:X35" si="18">SUM(W32:W34)</f>
+        <f t="shared" ref="W35:X35" si="19">SUM(W32:W34)</f>
         <v>2354</v>
       </c>
       <c r="X35" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2358</v>
       </c>
       <c r="Y35" s="6">
-        <f t="shared" ref="Y35:AD35" si="19">Y31*(1-Y53)</f>
+        <f t="shared" ref="Y35:AD35" si="20">Y31*(1-Y53)</f>
         <v>2595.9999999999995</v>
       </c>
       <c r="Z35" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2825.8911999999996</v>
       </c>
       <c r="AA35" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2755.1842515999997</v>
       </c>
       <c r="AB35" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3036.1636822440005</v>
       </c>
       <c r="AC35" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3346.6906024459604</v>
       </c>
       <c r="AD35" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3689.9843481860967</v>
       </c>
     </row>
@@ -3076,27 +3250,27 @@
         <v>4711</v>
       </c>
       <c r="E36" s="6">
-        <f t="shared" ref="E36:J36" si="20">E31-E35</f>
+        <f t="shared" ref="E36:J36" si="21">E31-E35</f>
         <v>0</v>
       </c>
       <c r="F36" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="G36" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5710</v>
       </c>
       <c r="H36" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5235</v>
       </c>
       <c r="I36" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5251</v>
       </c>
       <c r="J36" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5356.02</v>
       </c>
       <c r="K36" s="6"/>
@@ -3112,35 +3286,35 @@
         <v>15441</v>
       </c>
       <c r="W36" s="6">
-        <f t="shared" ref="W36:X36" si="21">W31-W35</f>
+        <f t="shared" ref="W36:X36" si="22">W31-W35</f>
         <v>17055</v>
       </c>
       <c r="X36" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>19147</v>
       </c>
       <c r="Y36" s="6">
-        <f t="shared" ref="Y36" si="22">Y31-Y35</f>
+        <f t="shared" ref="Y36" si="23">Y31-Y35</f>
         <v>21004</v>
       </c>
       <c r="Z36" s="6">
-        <f t="shared" ref="Z36" si="23">Z31-Z35</f>
+        <f t="shared" ref="Z36" si="24">Z31-Z35</f>
         <v>22864.0288</v>
       </c>
       <c r="AA36" s="6">
-        <f t="shared" ref="AA36" si="24">AA31-AA35</f>
+        <f t="shared" ref="AA36" si="25">AA31-AA35</f>
         <v>22291.945308400002</v>
       </c>
       <c r="AB36" s="6">
-        <f t="shared" ref="AB36" si="25">AB31-AB35</f>
+        <f t="shared" ref="AB36" si="26">AB31-AB35</f>
         <v>24565.324338156006</v>
       </c>
       <c r="AC36" s="6">
-        <f t="shared" ref="AC36:AD36" si="26">AC31-AC35</f>
+        <f t="shared" ref="AC36:AD36" si="27">AC31-AC35</f>
         <v>27077.769419790046</v>
       </c>
       <c r="AD36" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>29855.327908051149</v>
       </c>
     </row>
@@ -3158,11 +3332,11 @@
         <v>1082</v>
       </c>
       <c r="I37" s="6">
-        <f t="shared" ref="I37:J39" si="27">H37*1.01</f>
+        <f t="shared" ref="I37:J39" si="28">H37*1.01</f>
         <v>1092.82</v>
       </c>
       <c r="J37" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1103.7482</v>
       </c>
       <c r="K37" s="6"/>
@@ -3201,11 +3375,11 @@
         <v>1626</v>
       </c>
       <c r="I38" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1642.26</v>
       </c>
       <c r="J38" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1658.6826000000001</v>
       </c>
       <c r="K38" s="6"/>
@@ -3234,19 +3408,19 @@
         <v>6723.1296000000011</v>
       </c>
       <c r="AA38" s="6">
-        <f t="shared" ref="AA38:AD38" si="28">Z38*1.08</f>
+        <f t="shared" ref="AA38:AD38" si="29">Z38*1.08</f>
         <v>7260.9799680000015</v>
       </c>
       <c r="AB38" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>7841.8583654400018</v>
       </c>
       <c r="AC38" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>8469.2070346752025</v>
       </c>
       <c r="AD38" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>9146.74359744922</v>
       </c>
     </row>
@@ -3264,11 +3438,11 @@
         <v>377</v>
       </c>
       <c r="I39" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>380.77</v>
       </c>
       <c r="J39" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>384.57769999999999</v>
       </c>
       <c r="K39" s="6"/>
@@ -3297,19 +3471,19 @@
         <v>1783.4256000000003</v>
       </c>
       <c r="AA39" s="6">
-        <f t="shared" ref="AA39:AD39" si="29">Z39*1.08</f>
+        <f t="shared" ref="AA39:AD39" si="30">Z39*1.08</f>
         <v>1926.0996480000003</v>
       </c>
       <c r="AB39" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2080.1876198400005</v>
       </c>
       <c r="AC39" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2246.6026294272006</v>
       </c>
       <c r="AD39" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2426.3308397813767</v>
       </c>
     </row>
@@ -3322,31 +3496,31 @@
         <v>0</v>
       </c>
       <c r="D40" s="6">
-        <f t="shared" ref="D40:J40" si="30">SUM(D37:D39)</f>
+        <f t="shared" ref="D40:J40" si="31">SUM(D37:D39)</f>
         <v>2784</v>
       </c>
       <c r="E40" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="F40" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G40" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H40" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>3085</v>
       </c>
       <c r="I40" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>3115.85</v>
       </c>
       <c r="J40" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>3147.0084999999999</v>
       </c>
       <c r="K40" s="6"/>
@@ -3374,15 +3548,15 @@
         <v>9174</v>
       </c>
       <c r="W40" s="6">
-        <f t="shared" ref="W40:Y40" si="31">SUM(W37:W39)</f>
+        <f t="shared" ref="W40:Y40" si="32">SUM(W37:W39)</f>
         <v>10237</v>
       </c>
       <c r="X40" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>11237</v>
       </c>
       <c r="Y40" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>12204.661343873518</v>
       </c>
       <c r="Z40" s="6">
@@ -3390,19 +3564,19 @@
         <v>13261.136703999999</v>
       </c>
       <c r="AA40" s="6">
-        <f t="shared" ref="AA40:AD40" si="32">AA36*0.58</f>
+        <f t="shared" ref="AA40:AD40" si="33">AA36*0.58</f>
         <v>12929.328278872001</v>
       </c>
       <c r="AB40" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>14247.888116130482</v>
       </c>
       <c r="AC40" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>15705.106263478225</v>
       </c>
       <c r="AD40" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>17316.090186669666</v>
       </c>
     </row>
@@ -3415,31 +3589,31 @@
         <v>0</v>
       </c>
       <c r="D41" s="6">
-        <f t="shared" ref="D41:J41" si="33">D36-D40</f>
+        <f t="shared" ref="D41:J41" si="34">D36-D40</f>
         <v>1927</v>
       </c>
       <c r="E41" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="F41" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="G41" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>5710</v>
       </c>
       <c r="H41" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2150</v>
       </c>
       <c r="I41" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2135.15</v>
       </c>
       <c r="J41" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2209.0115000000005</v>
       </c>
       <c r="K41" s="6"/>
@@ -3467,35 +3641,35 @@
         <v>6267</v>
       </c>
       <c r="W41" s="6">
-        <f t="shared" ref="W41:AC41" si="34">W36-W40</f>
+        <f t="shared" ref="W41:AC41" si="35">W36-W40</f>
         <v>6818</v>
       </c>
       <c r="X41" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7910</v>
       </c>
       <c r="Y41" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>8799.3386561264815</v>
       </c>
       <c r="Z41" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>9602.8920960000014</v>
       </c>
       <c r="AA41" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>9362.6170295280008</v>
       </c>
       <c r="AB41" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>10317.436222025524</v>
       </c>
       <c r="AC41" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>11372.663156311821</v>
       </c>
       <c r="AD41" s="6">
-        <f t="shared" ref="AD41" si="35">AD36-AD40</f>
+        <f t="shared" ref="AD41" si="36">AD36-AD40</f>
         <v>12539.237721381483</v>
       </c>
       <c r="AE41" s="6">
@@ -3572,31 +3746,31 @@
         <v>0</v>
       </c>
       <c r="D43" s="6">
-        <f t="shared" ref="D43:J43" si="36">D41+D42</f>
+        <f t="shared" ref="D43:J43" si="37">D41+D42</f>
         <v>1927</v>
       </c>
       <c r="E43" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="F43" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="G43" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5710</v>
       </c>
       <c r="H43" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2150</v>
       </c>
       <c r="I43" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2120.8475000000003</v>
       </c>
       <c r="J43" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2207.4340850000003</v>
       </c>
       <c r="K43" s="6"/>
@@ -3624,35 +3798,35 @@
         <v>6136</v>
       </c>
       <c r="W43" s="6">
-        <f t="shared" ref="W43:AC43" si="37">W41+W42</f>
+        <f t="shared" ref="W43:AC43" si="38">W41+W42</f>
         <v>6721</v>
       </c>
       <c r="X43" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>7789</v>
       </c>
       <c r="Y43" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>8783.458741126482</v>
       </c>
       <c r="Z43" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>9649.5608540400008</v>
       </c>
       <c r="AA43" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>9637.9803798087487</v>
       </c>
       <c r="AB43" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>10821.21970730774</v>
       </c>
       <c r="AC43" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>12132.90954865723</v>
       </c>
       <c r="AD43" s="6">
-        <f t="shared" ref="AD43" si="38">AD41+AD42</f>
+        <f t="shared" ref="AD43" si="39">AD41+AD42</f>
         <v>13587.034070030069</v>
       </c>
       <c r="AE43" s="6">
@@ -3688,27 +3862,27 @@
       <c r="X44" s="14"/>
       <c r="Y44" s="14"/>
       <c r="Z44" s="6">
-        <f t="shared" ref="Z44:AE44" si="39">Z43*0.21</f>
+        <f t="shared" ref="Z44:AE44" si="40">Z43*0.21</f>
         <v>2026.4077793484</v>
       </c>
       <c r="AA44" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2023.9758797598372</v>
       </c>
       <c r="AB44" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2272.4561385346256</v>
       </c>
       <c r="AC44" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2547.9110052180181</v>
       </c>
       <c r="AD44" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2853.2771547063144</v>
       </c>
       <c r="AE44" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2659.5723207050128</v>
       </c>
     </row>
@@ -3721,31 +3895,31 @@
         <v>0</v>
       </c>
       <c r="D45" s="10">
-        <f t="shared" ref="D45:J45" si="40">D43-D44</f>
+        <f t="shared" ref="D45:J45" si="41">D43-D44</f>
         <v>1927</v>
       </c>
       <c r="E45" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="F45" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="G45" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>5710</v>
       </c>
       <c r="H45" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2150</v>
       </c>
       <c r="I45" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1696.6780000000003</v>
       </c>
       <c r="J45" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1765.9472680000003</v>
       </c>
       <c r="S45" s="10">
@@ -3765,39 +3939,39 @@
         <v>6136</v>
       </c>
       <c r="W45" s="10">
-        <f t="shared" ref="W45:X45" si="41">W43-W44</f>
+        <f t="shared" ref="W45:X45" si="42">W43-W44</f>
         <v>6721</v>
       </c>
       <c r="X45" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>7789</v>
       </c>
       <c r="Y45" s="10">
-        <f t="shared" ref="Y45" si="42">Y43-Y44</f>
+        <f t="shared" ref="Y45" si="43">Y43-Y44</f>
         <v>8783.458741126482</v>
       </c>
       <c r="Z45" s="10">
-        <f t="shared" ref="Z45" si="43">Z43-Z44</f>
+        <f t="shared" ref="Z45" si="44">Z43-Z44</f>
         <v>7623.1530746916005</v>
       </c>
       <c r="AA45" s="10">
-        <f t="shared" ref="AA45" si="44">AA43-AA44</f>
+        <f t="shared" ref="AA45" si="45">AA43-AA44</f>
         <v>7614.0045000489117</v>
       </c>
       <c r="AB45" s="10">
-        <f t="shared" ref="AB45" si="45">AB43-AB44</f>
+        <f t="shared" ref="AB45" si="46">AB43-AB44</f>
         <v>8548.7635687731145</v>
       </c>
       <c r="AC45" s="10">
-        <f t="shared" ref="AC45:AE45" si="46">AC43-AC44</f>
+        <f t="shared" ref="AC45:AE45" si="47">AC43-AC44</f>
         <v>9584.9985434392111</v>
       </c>
       <c r="AD45" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>10733.756915323755</v>
       </c>
       <c r="AE45" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>10005.057777890286</v>
       </c>
     </row>
@@ -3857,35 +4031,35 @@
         <v>23</v>
       </c>
       <c r="C47" s="9" t="e">
-        <f t="shared" ref="C47:J47" si="47">C45/C46</f>
+        <f t="shared" ref="C47:J47" si="48">C45/C46</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D47" s="9" t="e">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E47" s="9" t="e">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F47" s="9" t="e">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G47" s="9" t="e">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H47" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.0683639792550688</v>
       </c>
       <c r="I47" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>3.9997123998114108</v>
       </c>
       <c r="J47" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>4.1630062894860922</v>
       </c>
       <c r="K47" s="9"/>
@@ -3913,35 +4087,35 @@
         <v>13.027600849256901</v>
       </c>
       <c r="W47" s="9">
-        <f t="shared" ref="W47:AC47" si="48">W45/W46</f>
+        <f t="shared" ref="W47:AC47" si="49">W45/W46</f>
         <v>14.642701525054466</v>
       </c>
       <c r="X47" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>17.308888888888887</v>
       </c>
       <c r="Y47" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>21.370945842156889</v>
       </c>
       <c r="Z47" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>18.547817699979564</v>
       </c>
       <c r="AA47" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>18.525558394279592</v>
       </c>
       <c r="AB47" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>20.799911359545291</v>
       </c>
       <c r="AC47" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>23.321164339268154</v>
       </c>
       <c r="AD47" s="9">
-        <f t="shared" ref="AD47" si="49">AD45/AD46</f>
+        <f t="shared" ref="AD47" si="50">AD45/AD46</f>
         <v>26.116196874267043</v>
       </c>
       <c r="AE47" s="9"/>
@@ -4004,27 +4178,27 @@
         <v>0.10799113813179462</v>
       </c>
       <c r="Y49" s="12">
-        <f t="shared" ref="Y49:AE49" si="50">Y31/X31-1</f>
+        <f t="shared" ref="Y49:AE49" si="51">Y31/X31-1</f>
         <v>9.7419204836084683E-2</v>
       </c>
       <c r="Z49" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>8.8555932203389753E-2</v>
       </c>
       <c r="AA49" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-2.5021114896426222E-2</v>
       </c>
       <c r="AB49" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.10198208358690697</v>
       </c>
       <c r="AC49" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.10227608017906742</v>
       </c>
       <c r="AD49" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.10257707882803291</v>
       </c>
       <c r="AE49" s="12"/>
@@ -4038,31 +4212,31 @@
       </c>
       <c r="C50" s="12"/>
       <c r="D50" s="12" t="e">
-        <f t="shared" ref="D50:J50" si="51">D31/C31-1</f>
+        <f t="shared" ref="D50:J50" si="52">D31/C31-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E50" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>-1</v>
       </c>
       <c r="F50" s="12" t="e">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G50" s="12" t="e">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H50" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>2.8546409807355566E-2</v>
       </c>
       <c r="I50" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>4.5973097224587534E-3</v>
       </c>
       <c r="J50" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="K50" s="12"/>
@@ -4091,27 +4265,27 @@
         <v>57</v>
       </c>
       <c r="T51" s="12" t="e">
-        <f t="shared" ref="T51:Y51" si="52">SUM(T38:T39)/SUM(S38:S39)-1</f>
+        <f t="shared" ref="T51:Y51" si="53">SUM(T38:T39)/SUM(S38:S39)-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U51" s="12" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V51" s="12" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W51" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>9.326006141910459E-2</v>
       </c>
       <c r="X51" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>7.820816085156701E-2</v>
       </c>
       <c r="Y51" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="Z51" s="12"/>
@@ -4141,23 +4315,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D53" s="13">
-        <f t="shared" ref="D53:H53" si="53">D36/D31</f>
+        <f t="shared" ref="D53:H53" si="54">D36/D31</f>
         <v>0.88736108495008481</v>
       </c>
       <c r="E53" s="13" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F53" s="13" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G53" s="13">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>1</v>
       </c>
       <c r="H53" s="13">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.89136727396560533</v>
       </c>
       <c r="I53" s="13">
@@ -4214,35 +4388,35 @@
         <v>34</v>
       </c>
       <c r="C54" s="14" t="e">
-        <f t="shared" ref="C54:J54" si="54">C41/C31</f>
+        <f t="shared" ref="C54:J54" si="55">C41/C31</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D54" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.36296854398191752</v>
       </c>
       <c r="E54" s="14" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F54" s="14" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G54" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="H54" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.36608207049208241</v>
       </c>
       <c r="I54" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.36188983050847462</v>
       </c>
       <c r="J54" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.36706738118976412</v>
       </c>
       <c r="K54" s="14"/>
@@ -4254,39 +4428,39 @@
       <c r="Q54" s="14"/>
       <c r="R54" s="14"/>
       <c r="V54" s="14">
-        <f t="shared" ref="V54:AD54" si="55">V41/V31</f>
+        <f t="shared" ref="V54:AD54" si="56">V41/V31</f>
         <v>0.35595819606952173</v>
       </c>
       <c r="W54" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.35128033386573237</v>
       </c>
       <c r="X54" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.36782143687514529</v>
       </c>
       <c r="Y54" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.37285333288671529</v>
       </c>
       <c r="Z54" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.37380000000000008</v>
       </c>
       <c r="AA54" s="14">
-        <f t="shared" si="55"/>
+        <f>AA41/AA31</f>
         <v>0.37380000000000002</v>
       </c>
       <c r="AB54" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.37380000000000008</v>
       </c>
       <c r="AC54" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.37380000000000008</v>
       </c>
       <c r="AD54" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.37380000000000002</v>
       </c>
       <c r="AE54" s="14"/>
@@ -4295,7 +4469,7 @@
       <c r="AH54" s="14"/>
     </row>
     <row r="56" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B56" s="38" t="s">
+      <c r="B56" s="37" t="s">
         <v>27</v>
       </c>
       <c r="C56" s="6">
@@ -4338,7 +4512,7 @@
       <c r="P56" s="6"/>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
-      <c r="U56" s="38"/>
+      <c r="U56" s="37"/>
       <c r="W56" s="6">
         <f>W57-SUM(W68,W72)</f>
         <v>2674</v>
@@ -4352,28 +4526,28 @@
         <v>1555.6252680000007</v>
       </c>
       <c r="Z56" s="6">
-        <f t="shared" ref="Z56:AD56" si="56">Y56+Z45</f>
+        <f t="shared" ref="Z56:AD56" si="57">Y56+Z45</f>
         <v>9178.7783426916012</v>
       </c>
       <c r="AA56" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>16792.782842740511</v>
       </c>
       <c r="AB56" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>25341.546411513627</v>
       </c>
       <c r="AC56" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>34926.544954952842</v>
       </c>
       <c r="AD56" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>45660.301870276598</v>
       </c>
     </row>
     <row r="57" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B57" s="38" t="s">
+      <c r="B57" s="37" t="s">
         <v>3</v>
       </c>
       <c r="G57" s="6">
@@ -4384,7 +4558,7 @@
         <f>4931+782</f>
         <v>5713</v>
       </c>
-      <c r="U57" s="38"/>
+      <c r="U57" s="37"/>
       <c r="W57" s="6">
         <f>7141+701</f>
         <v>7842</v>
@@ -4394,7 +4568,7 @@
       </c>
     </row>
     <row r="58" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B58" s="38" t="s">
+      <c r="B58" s="37" t="s">
         <v>104</v>
       </c>
       <c r="G58" s="6">
@@ -4405,7 +4579,7 @@
         <f>6166+114+477+323+540</f>
         <v>7620</v>
       </c>
-      <c r="U58" s="38"/>
+      <c r="U58" s="37"/>
       <c r="W58" s="6">
         <v>2224</v>
       </c>
@@ -4414,10 +4588,10 @@
       </c>
     </row>
     <row r="59" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B59" s="38" t="s">
+      <c r="B59" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="U59" s="38"/>
+      <c r="U59" s="37"/>
       <c r="W59" s="6">
         <v>1018</v>
       </c>
@@ -4426,10 +4600,10 @@
       </c>
     </row>
     <row r="60" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B60" s="38" t="s">
+      <c r="B60" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="U60" s="38"/>
+      <c r="U60" s="37"/>
       <c r="W60" s="6">
         <v>358</v>
       </c>
@@ -4438,10 +4612,10 @@
       </c>
     </row>
     <row r="61" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B61" s="38" t="s">
+      <c r="B61" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="U61" s="38"/>
+      <c r="U61" s="37"/>
       <c r="W61" s="6">
         <v>12805</v>
       </c>
@@ -4450,10 +4624,10 @@
       </c>
     </row>
     <row r="62" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B62" s="38" t="s">
+      <c r="B62" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="U62" s="38"/>
+      <c r="U62" s="37"/>
       <c r="W62" s="6">
         <v>1088</v>
       </c>
@@ -4462,10 +4636,10 @@
       </c>
     </row>
     <row r="63" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B63" s="38" t="s">
+      <c r="B63" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="U63" s="38"/>
+      <c r="U63" s="37"/>
       <c r="W63" s="6">
         <v>1191</v>
       </c>
@@ -4474,10 +4648,10 @@
       </c>
     </row>
     <row r="64" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B64" s="38" t="s">
+      <c r="B64" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="U64" s="38"/>
+      <c r="U64" s="37"/>
       <c r="W64" s="6">
         <v>2030</v>
       </c>
@@ -4486,10 +4660,10 @@
       </c>
     </row>
     <row r="65" spans="2:35" x14ac:dyDescent="0.2">
-      <c r="B65" s="38" t="s">
+      <c r="B65" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="U65" s="38"/>
+      <c r="U65" s="37"/>
       <c r="W65" s="6">
         <v>1223</v>
       </c>
@@ -4498,10 +4672,10 @@
       </c>
     </row>
     <row r="66" spans="2:35" x14ac:dyDescent="0.2">
-      <c r="B66" s="38" t="s">
+      <c r="B66" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="U66" s="38"/>
+      <c r="U66" s="37"/>
       <c r="W66" s="6">
         <f>SUM(W57:W65)</f>
         <v>29779</v>
@@ -4517,7 +4691,7 @@
       <c r="AC67" s="14"/>
     </row>
     <row r="68" spans="2:35" x14ac:dyDescent="0.2">
-      <c r="B68" s="38" t="s">
+      <c r="B68" s="37" t="s">
         <v>4</v>
       </c>
       <c r="W68" s="6">
@@ -4530,7 +4704,7 @@
       </c>
     </row>
     <row r="69" spans="2:35" x14ac:dyDescent="0.2">
-      <c r="B69" s="38" t="s">
+      <c r="B69" s="37" t="s">
         <v>53</v>
       </c>
       <c r="W69" s="6">
@@ -4544,28 +4718,28 @@
         <v>403.82222222222214</v>
       </c>
       <c r="Z69" s="6">
-        <f t="shared" ref="Z69:AD69" si="57">(Z35/360)*56</f>
+        <f t="shared" ref="Z69:AD69" si="58">(Z35/360)*56</f>
         <v>439.58307555555547</v>
       </c>
       <c r="AA69" s="6">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>428.58421691555549</v>
       </c>
       <c r="AB69" s="6">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>472.29212834906679</v>
       </c>
       <c r="AC69" s="6">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>520.59631593603831</v>
       </c>
       <c r="AD69" s="6">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>573.99756527339287</v>
       </c>
     </row>
     <row r="70" spans="2:35" x14ac:dyDescent="0.2">
-      <c r="B70" s="38" t="s">
+      <c r="B70" s="37" t="s">
         <v>108</v>
       </c>
       <c r="W70" s="6">
@@ -4575,7 +4749,7 @@
         <v>2336</v>
       </c>
       <c r="Y70" s="6">
-        <f t="shared" ref="Y70:AD70" si="58">0.3*SUM(Y38:Y39)</f>
+        <f t="shared" ref="Y70:AD70" si="59">0.3*SUM(Y38:Y39)</f>
         <v>2362.9320000000002</v>
       </c>
       <c r="Z70" s="6">
@@ -4583,24 +4757,24 @@
         <v>2551.9665600000003</v>
       </c>
       <c r="AA70" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>2756.1238848000007</v>
       </c>
       <c r="AB70" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>2976.6137955840004</v>
       </c>
       <c r="AC70" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>3214.7428992307205</v>
       </c>
       <c r="AD70" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>3471.922331169179</v>
       </c>
     </row>
     <row r="71" spans="2:35" x14ac:dyDescent="0.2">
-      <c r="B71" s="38" t="s">
+      <c r="B71" s="37" t="s">
         <v>54</v>
       </c>
       <c r="W71" s="6">
@@ -4614,28 +4788,28 @@
         <v>7080</v>
       </c>
       <c r="Z71" s="6">
-        <f t="shared" ref="Z71:AD71" si="59">0.3*Z31</f>
+        <f t="shared" ref="Z71:AD71" si="60">0.3*Z31</f>
         <v>7706.9759999999987</v>
       </c>
       <c r="AA71" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>7514.138868</v>
       </c>
       <c r="AB71" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>8280.4464061200015</v>
       </c>
       <c r="AC71" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>9127.3380066708014</v>
       </c>
       <c r="AD71" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>10063.593676871173</v>
       </c>
     </row>
     <row r="72" spans="2:35" x14ac:dyDescent="0.2">
-      <c r="B72" s="38" t="s">
+      <c r="B72" s="37" t="s">
         <v>109</v>
       </c>
       <c r="W72" s="6">
@@ -4646,7 +4820,7 @@
       </c>
     </row>
     <row r="73" spans="2:35" x14ac:dyDescent="0.2">
-      <c r="B73" s="38" t="s">
+      <c r="B73" s="37" t="s">
         <v>40</v>
       </c>
       <c r="W73" s="6">
@@ -4659,7 +4833,7 @@
       </c>
     </row>
     <row r="74" spans="2:35" x14ac:dyDescent="0.2">
-      <c r="B74" s="38" t="s">
+      <c r="B74" s="37" t="s">
         <v>39</v>
       </c>
       <c r="W74" s="6">
@@ -4672,7 +4846,7 @@
       </c>
     </row>
     <row r="75" spans="2:35" x14ac:dyDescent="0.2">
-      <c r="B75" s="38" t="s">
+      <c r="B75" s="37" t="s">
         <v>41</v>
       </c>
       <c r="W75" s="6">
@@ -4702,7 +4876,7 @@
       </c>
     </row>
     <row r="78" spans="2:35" x14ac:dyDescent="0.2">
-      <c r="B78" s="33" t="s">
+      <c r="B78" s="32" t="s">
         <v>120</v>
       </c>
       <c r="W78" s="6">
@@ -4714,27 +4888,27 @@
         <v>55.208156329651651</v>
       </c>
       <c r="Y78" s="6">
-        <f t="shared" ref="Y78:AD78" si="60">(Y69/X35)*360</f>
+        <f t="shared" ref="Y78:AD78" si="61">(Y69/X35)*360</f>
         <v>61.652247667514835</v>
       </c>
       <c r="Z78" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>60.959132203389828</v>
       </c>
       <c r="AA78" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>54.598817565800125</v>
       </c>
       <c r="AB78" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>61.710996680866799</v>
       </c>
       <c r="AC78" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>61.727460490027781</v>
       </c>
       <c r="AD78" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>61.744316414369848</v>
       </c>
     </row>
@@ -4752,47 +4926,47 @@
       <c r="B80" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="V80" s="33">
+      <c r="V80" s="32">
         <f>V45</f>
         <v>6136</v>
       </c>
-      <c r="W80" s="33">
+      <c r="W80" s="32">
         <f>W45</f>
         <v>6721</v>
       </c>
-      <c r="X80" s="33">
+      <c r="X80" s="32">
         <f>X45</f>
         <v>7789</v>
       </c>
-      <c r="Y80" s="33">
+      <c r="Y80" s="32">
         <f>Y45</f>
         <v>8783.458741126482</v>
       </c>
-      <c r="Z80" s="33">
+      <c r="Z80" s="32">
         <f>Z45</f>
         <v>7623.1530746916005</v>
       </c>
-      <c r="AA80" s="33">
+      <c r="AA80" s="32">
         <f>AA45</f>
         <v>7614.0045000489117</v>
       </c>
-      <c r="AB80" s="33">
+      <c r="AB80" s="32">
         <f>AB45</f>
         <v>8548.7635687731145</v>
       </c>
-      <c r="AC80" s="33">
+      <c r="AC80" s="32">
         <f>AC45</f>
         <v>9584.9985434392111</v>
       </c>
-      <c r="AD80" s="33">
+      <c r="AD80" s="32">
         <f>AD45</f>
         <v>10733.756915323755</v>
       </c>
-      <c r="AE80" s="33">
+      <c r="AE80" s="32">
         <f>AE45</f>
         <v>10005.057777890286</v>
       </c>
-      <c r="AI80" s="38"/>
+      <c r="AI80" s="37"/>
     </row>
     <row r="81" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B81" s="6" t="s">
@@ -4808,7 +4982,7 @@
         <v>5560</v>
       </c>
       <c r="Y81" s="14"/>
-      <c r="AI81" s="38"/>
+      <c r="AI81" s="37"/>
     </row>
     <row r="82" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B82" s="6" t="s">
@@ -4832,29 +5006,29 @@
         <v>1027.5968</v>
       </c>
       <c r="AA82" s="6">
-        <f t="shared" ref="AA82:AE82" si="61">0.04*AA31</f>
+        <f t="shared" ref="AA82:AE82" si="62">0.04*AA31</f>
         <v>1001.8851824000001</v>
       </c>
       <c r="AB82" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1104.0595208160003</v>
       </c>
       <c r="AC82" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1216.9784008894403</v>
       </c>
       <c r="AD82" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1341.8124902494899</v>
       </c>
       <c r="AE82" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1355.2306151519847</v>
       </c>
-      <c r="AI82" s="38"/>
+      <c r="AI82" s="37"/>
     </row>
     <row r="83" spans="2:36" x14ac:dyDescent="0.2">
-      <c r="B83" s="33" t="s">
+      <c r="B83" s="32" t="s">
         <v>103</v>
       </c>
       <c r="V83" s="6">
@@ -4870,10 +5044,10 @@
         <f>Y31*0.08</f>
         <v>1888</v>
       </c>
-      <c r="AI83" s="38"/>
+      <c r="AI83" s="37"/>
     </row>
     <row r="84" spans="2:36" x14ac:dyDescent="0.2">
-      <c r="B84" s="33" t="s">
+      <c r="B84" s="32" t="s">
         <v>102</v>
       </c>
       <c r="V84" s="6">
@@ -4889,10 +5063,10 @@
         <f>X84*(1+Y49)</f>
         <v>-513.59218786328768</v>
       </c>
-      <c r="AI84" s="38"/>
+      <c r="AI84" s="37"/>
     </row>
     <row r="85" spans="2:36" x14ac:dyDescent="0.2">
-      <c r="B85" s="33" t="s">
+      <c r="B85" s="32" t="s">
         <v>92</v>
       </c>
       <c r="V85" s="6">
@@ -4908,11 +5082,11 @@
         <f>X85*(1+Y49)</f>
         <v>-38.409672169262961</v>
       </c>
-      <c r="AI85" s="38"/>
+      <c r="AI85" s="37"/>
       <c r="AJ85" s="18"/>
     </row>
     <row r="86" spans="2:36" x14ac:dyDescent="0.2">
-      <c r="B86" s="33" t="s">
+      <c r="B86" s="32" t="s">
         <v>94</v>
       </c>
       <c r="V86" s="6">
@@ -4928,11 +5102,11 @@
         <f>X86*(1+Y49)</f>
         <v>10.974192048360846</v>
       </c>
-      <c r="AI86" s="38"/>
+      <c r="AI86" s="37"/>
       <c r="AJ86" s="18"/>
     </row>
     <row r="87" spans="2:36" x14ac:dyDescent="0.2">
-      <c r="B87" s="33" t="s">
+      <c r="B87" s="32" t="s">
         <v>90</v>
       </c>
       <c r="V87" s="6">
@@ -4940,46 +5114,46 @@
         <v>0</v>
       </c>
       <c r="W87" s="6">
-        <f t="shared" ref="W87:AE87" si="62">SUM(W69:W71)</f>
+        <f t="shared" ref="W87:AE87" si="63">SUM(W69:W71)</f>
         <v>8093</v>
       </c>
       <c r="X87" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>8828</v>
       </c>
       <c r="Y87" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>9846.7542222222219</v>
       </c>
       <c r="Z87" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>10698.525635555554</v>
       </c>
       <c r="AA87" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>10698.846969715556</v>
       </c>
       <c r="AB87" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>11729.352330053069</v>
       </c>
       <c r="AC87" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>12862.677221837559</v>
       </c>
       <c r="AD87" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>14109.513573313745</v>
       </c>
       <c r="AE87" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
-      <c r="AI87" s="38"/>
+      <c r="AI87" s="37"/>
       <c r="AJ87" s="18"/>
     </row>
     <row r="88" spans="2:36" x14ac:dyDescent="0.2">
-      <c r="B88" s="33" t="s">
+      <c r="B88" s="32" t="s">
         <v>25</v>
       </c>
       <c r="V88" s="6">
@@ -4987,11 +5161,11 @@
         <v>7419</v>
       </c>
       <c r="W88" s="6">
-        <f t="shared" ref="W88:X88" si="63">SUM(W81:W86)</f>
+        <f t="shared" ref="W88:X88" si="64">SUM(W81:W86)</f>
         <v>7585</v>
       </c>
       <c r="X88" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>7757</v>
       </c>
       <c r="Y88" s="6">
@@ -4999,33 +5173,33 @@
         <v>11070.919331686819</v>
       </c>
       <c r="Z88" s="6">
-        <f t="shared" ref="Z88:AE88" si="64">SUM(Z80:Z86)</f>
+        <f t="shared" ref="Z88:AE88" si="65">SUM(Z80:Z86)</f>
         <v>8650.7498746916008</v>
       </c>
       <c r="AA88" s="6">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>8615.8896824489111</v>
       </c>
       <c r="AB88" s="6">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>9652.8230895891138</v>
       </c>
       <c r="AC88" s="6">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>10801.976944328651</v>
       </c>
       <c r="AD88" s="6">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>12075.569405573244</v>
       </c>
       <c r="AE88" s="6">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>11360.28839304227</v>
       </c>
       <c r="AJ88" s="18"/>
     </row>
     <row r="89" spans="2:36" x14ac:dyDescent="0.2">
-      <c r="B89" s="33" t="s">
+      <c r="B89" s="32" t="s">
         <v>121</v>
       </c>
       <c r="X89" s="6">
@@ -5037,23 +5211,23 @@
         <v>1018.7542222222219</v>
       </c>
       <c r="Z89" s="6">
-        <f t="shared" ref="Z89:AD89" si="65">Z87-Y87</f>
+        <f t="shared" ref="Z89:AD89" si="66">Z87-Y87</f>
         <v>851.77141333333202</v>
       </c>
       <c r="AA89" s="6">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.3213341600021522</v>
       </c>
       <c r="AB89" s="6">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>1030.5053603375127</v>
       </c>
       <c r="AC89" s="6">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>1133.3248917844903</v>
       </c>
       <c r="AD89" s="6">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>1246.8363514761859</v>
       </c>
       <c r="AE89" s="6">
@@ -5070,7 +5244,7 @@
       <c r="AJ90" s="18"/>
     </row>
     <row r="91" spans="2:36" x14ac:dyDescent="0.2">
-      <c r="B91" s="38" t="s">
+      <c r="B91" s="37" t="s">
         <v>91</v>
       </c>
       <c r="V91" s="6">
@@ -5085,33 +5259,33 @@
       <c r="Y91" s="6">
         <v>-300</v>
       </c>
-      <c r="Z91" s="33">
+      <c r="Z91" s="32">
         <f>-0.02*Z31</f>
         <v>-513.79840000000002</v>
       </c>
-      <c r="AA91" s="33">
+      <c r="AA91" s="32">
         <f>-0.02*AA31</f>
         <v>-500.94259120000004</v>
       </c>
-      <c r="AB91" s="33">
+      <c r="AB91" s="32">
         <f>-0.02*AB31</f>
         <v>-552.02976040800013</v>
       </c>
-      <c r="AC91" s="33">
+      <c r="AC91" s="32">
         <f>-0.02*AC31</f>
         <v>-608.48920044472015</v>
       </c>
-      <c r="AD91" s="33">
+      <c r="AD91" s="32">
         <f>-0.02*AD31</f>
         <v>-670.90624512474494</v>
       </c>
-      <c r="AE91" s="33">
+      <c r="AE91" s="32">
         <f>-AE82</f>
         <v>-1355.2306151519847</v>
       </c>
     </row>
     <row r="92" spans="2:36" x14ac:dyDescent="0.2">
-      <c r="B92" s="38" t="s">
+      <c r="B92" s="37" t="s">
         <v>92</v>
       </c>
       <c r="V92" s="6">
@@ -5125,17 +5299,17 @@
       </c>
     </row>
     <row r="93" spans="2:36" x14ac:dyDescent="0.2">
-      <c r="B93" s="38" t="s">
+      <c r="B93" s="37" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="94" spans="2:36" x14ac:dyDescent="0.2">
-      <c r="B94" s="38" t="s">
+      <c r="B94" s="37" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="95" spans="2:36" x14ac:dyDescent="0.2">
-      <c r="B95" s="38" t="s">
+      <c r="B95" s="37" t="s">
         <v>95</v>
       </c>
       <c r="V95" s="6">
@@ -5143,39 +5317,39 @@
         <v>-570</v>
       </c>
       <c r="W95" s="6">
-        <f t="shared" ref="W95:AE95" si="66">SUM(W91:W94)</f>
+        <f t="shared" ref="W95:AE95" si="67">SUM(W91:W94)</f>
         <v>776</v>
       </c>
       <c r="X95" s="6">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>149</v>
       </c>
       <c r="Y95" s="6">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>-300</v>
       </c>
       <c r="Z95" s="6">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>-513.79840000000002</v>
       </c>
       <c r="AA95" s="6">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>-500.94259120000004</v>
       </c>
       <c r="AB95" s="6">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>-552.02976040800013</v>
       </c>
       <c r="AC95" s="6">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>-608.48920044472015</v>
       </c>
       <c r="AD95" s="6">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>-670.90624512474494</v>
       </c>
       <c r="AE95" s="6">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>-1355.2306151519847</v>
       </c>
     </row>
@@ -5192,7 +5366,7 @@
       <c r="AE96" s="14"/>
     </row>
     <row r="97" spans="2:131" x14ac:dyDescent="0.2">
-      <c r="B97" s="38" t="s">
+      <c r="B97" s="37" t="s">
         <v>96</v>
       </c>
       <c r="V97" s="14"/>
@@ -5210,106 +5384,106 @@
       <c r="AH97" s="14">
         <v>0.03</v>
       </c>
-      <c r="AI97" s="24"/>
-      <c r="AJ97" s="24"/>
-      <c r="AK97" s="24"/>
-      <c r="AL97" s="24"/>
-      <c r="AM97" s="24"/>
-      <c r="AN97" s="24"/>
-      <c r="AO97" s="24"/>
-      <c r="AP97" s="24"/>
-      <c r="AQ97" s="24"/>
-      <c r="AR97" s="24"/>
-      <c r="AS97" s="24"/>
-      <c r="AT97" s="24"/>
-      <c r="AU97" s="24"/>
-      <c r="AV97" s="24"/>
-      <c r="AW97" s="24"/>
-      <c r="AX97" s="24"/>
-      <c r="AY97" s="24"/>
-      <c r="AZ97" s="24"/>
-      <c r="BA97" s="24"/>
-      <c r="BB97" s="24"/>
-      <c r="BC97" s="24"/>
-      <c r="BD97" s="24"/>
-      <c r="BE97" s="24"/>
-      <c r="BF97" s="24"/>
-      <c r="BG97" s="24"/>
-      <c r="BH97" s="24"/>
-      <c r="BI97" s="24"/>
-      <c r="BJ97" s="24"/>
-      <c r="BK97" s="24"/>
-      <c r="BL97" s="24"/>
-      <c r="BM97" s="24"/>
-      <c r="BN97" s="24"/>
-      <c r="BO97" s="24"/>
-      <c r="BP97" s="24"/>
-      <c r="BQ97" s="24"/>
-      <c r="BR97" s="24"/>
-      <c r="BS97" s="24"/>
-      <c r="BT97" s="24"/>
-      <c r="BU97" s="24"/>
-      <c r="BV97" s="24"/>
-      <c r="BW97" s="24"/>
-      <c r="BX97" s="24"/>
-      <c r="BY97" s="24"/>
-      <c r="BZ97" s="24"/>
-      <c r="CA97" s="24"/>
-      <c r="CB97" s="24"/>
-      <c r="CC97" s="24"/>
-      <c r="CD97" s="24"/>
-      <c r="CE97" s="24"/>
-      <c r="CF97" s="24"/>
-      <c r="CG97" s="24"/>
-      <c r="CH97" s="24"/>
-      <c r="CI97" s="24"/>
-      <c r="CJ97" s="24"/>
-      <c r="CK97" s="24"/>
-      <c r="CL97" s="24"/>
-      <c r="CM97" s="24"/>
-      <c r="CN97" s="24"/>
-      <c r="CO97" s="24"/>
-      <c r="CP97" s="24"/>
-      <c r="CQ97" s="24"/>
-      <c r="CR97" s="24"/>
-      <c r="CS97" s="24"/>
-      <c r="CT97" s="24"/>
-      <c r="CU97" s="24"/>
-      <c r="CV97" s="24"/>
-      <c r="CW97" s="24"/>
-      <c r="CX97" s="24"/>
-      <c r="CY97" s="24"/>
-      <c r="CZ97" s="24"/>
-      <c r="DA97" s="24"/>
-      <c r="DB97" s="24"/>
-      <c r="DC97" s="24"/>
-      <c r="DD97" s="24"/>
-      <c r="DE97" s="24"/>
-      <c r="DF97" s="24"/>
-      <c r="DG97" s="24"/>
-      <c r="DH97" s="24"/>
-      <c r="DI97" s="24"/>
-      <c r="DJ97" s="24"/>
-      <c r="DK97" s="24"/>
-      <c r="DL97" s="24"/>
-      <c r="DM97" s="24"/>
-      <c r="DN97" s="24"/>
-      <c r="DO97" s="24"/>
-      <c r="DP97" s="24"/>
-      <c r="DQ97" s="24"/>
-      <c r="DR97" s="24"/>
-      <c r="DS97" s="24"/>
-      <c r="DT97" s="24"/>
-      <c r="DU97" s="24"/>
-      <c r="DV97" s="24"/>
-      <c r="DW97" s="24"/>
-      <c r="DX97" s="24"/>
-      <c r="DY97" s="24"/>
-      <c r="DZ97" s="24"/>
-      <c r="EA97" s="24"/>
+      <c r="AI97" s="23"/>
+      <c r="AJ97" s="23"/>
+      <c r="AK97" s="23"/>
+      <c r="AL97" s="23"/>
+      <c r="AM97" s="23"/>
+      <c r="AN97" s="23"/>
+      <c r="AO97" s="23"/>
+      <c r="AP97" s="23"/>
+      <c r="AQ97" s="23"/>
+      <c r="AR97" s="23"/>
+      <c r="AS97" s="23"/>
+      <c r="AT97" s="23"/>
+      <c r="AU97" s="23"/>
+      <c r="AV97" s="23"/>
+      <c r="AW97" s="23"/>
+      <c r="AX97" s="23"/>
+      <c r="AY97" s="23"/>
+      <c r="AZ97" s="23"/>
+      <c r="BA97" s="23"/>
+      <c r="BB97" s="23"/>
+      <c r="BC97" s="23"/>
+      <c r="BD97" s="23"/>
+      <c r="BE97" s="23"/>
+      <c r="BF97" s="23"/>
+      <c r="BG97" s="23"/>
+      <c r="BH97" s="23"/>
+      <c r="BI97" s="23"/>
+      <c r="BJ97" s="23"/>
+      <c r="BK97" s="23"/>
+      <c r="BL97" s="23"/>
+      <c r="BM97" s="23"/>
+      <c r="BN97" s="23"/>
+      <c r="BO97" s="23"/>
+      <c r="BP97" s="23"/>
+      <c r="BQ97" s="23"/>
+      <c r="BR97" s="23"/>
+      <c r="BS97" s="23"/>
+      <c r="BT97" s="23"/>
+      <c r="BU97" s="23"/>
+      <c r="BV97" s="23"/>
+      <c r="BW97" s="23"/>
+      <c r="BX97" s="23"/>
+      <c r="BY97" s="23"/>
+      <c r="BZ97" s="23"/>
+      <c r="CA97" s="23"/>
+      <c r="CB97" s="23"/>
+      <c r="CC97" s="23"/>
+      <c r="CD97" s="23"/>
+      <c r="CE97" s="23"/>
+      <c r="CF97" s="23"/>
+      <c r="CG97" s="23"/>
+      <c r="CH97" s="23"/>
+      <c r="CI97" s="23"/>
+      <c r="CJ97" s="23"/>
+      <c r="CK97" s="23"/>
+      <c r="CL97" s="23"/>
+      <c r="CM97" s="23"/>
+      <c r="CN97" s="23"/>
+      <c r="CO97" s="23"/>
+      <c r="CP97" s="23"/>
+      <c r="CQ97" s="23"/>
+      <c r="CR97" s="23"/>
+      <c r="CS97" s="23"/>
+      <c r="CT97" s="23"/>
+      <c r="CU97" s="23"/>
+      <c r="CV97" s="23"/>
+      <c r="CW97" s="23"/>
+      <c r="CX97" s="23"/>
+      <c r="CY97" s="23"/>
+      <c r="CZ97" s="23"/>
+      <c r="DA97" s="23"/>
+      <c r="DB97" s="23"/>
+      <c r="DC97" s="23"/>
+      <c r="DD97" s="23"/>
+      <c r="DE97" s="23"/>
+      <c r="DF97" s="23"/>
+      <c r="DG97" s="23"/>
+      <c r="DH97" s="23"/>
+      <c r="DI97" s="23"/>
+      <c r="DJ97" s="23"/>
+      <c r="DK97" s="23"/>
+      <c r="DL97" s="23"/>
+      <c r="DM97" s="23"/>
+      <c r="DN97" s="23"/>
+      <c r="DO97" s="23"/>
+      <c r="DP97" s="23"/>
+      <c r="DQ97" s="23"/>
+      <c r="DR97" s="23"/>
+      <c r="DS97" s="23"/>
+      <c r="DT97" s="23"/>
+      <c r="DU97" s="23"/>
+      <c r="DV97" s="23"/>
+      <c r="DW97" s="23"/>
+      <c r="DX97" s="23"/>
+      <c r="DY97" s="23"/>
+      <c r="DZ97" s="23"/>
+      <c r="EA97" s="23"/>
     </row>
     <row r="98" spans="2:131" x14ac:dyDescent="0.2">
-      <c r="B98" s="38" t="s">
+      <c r="B98" s="37" t="s">
         <v>97</v>
       </c>
       <c r="AG98" s="6" t="s">
@@ -5320,7 +5494,7 @@
       </c>
     </row>
     <row r="99" spans="2:131" x14ac:dyDescent="0.2">
-      <c r="B99" s="38" t="s">
+      <c r="B99" s="37" t="s">
         <v>98</v>
       </c>
       <c r="AG99" s="6" t="s">
@@ -5331,19 +5505,19 @@
       </c>
     </row>
     <row r="100" spans="2:131" x14ac:dyDescent="0.2">
-      <c r="B100" s="38" t="s">
+      <c r="B100" s="37" t="s">
         <v>94</v>
       </c>
       <c r="AG100" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AH100" s="22">
+      <c r="AH100" s="21">
         <f>NPV(AH99,Z105:DI105)+Main!K5-Main!K6</f>
         <v>120626.04386399603</v>
       </c>
     </row>
     <row r="101" spans="2:131" x14ac:dyDescent="0.2">
-      <c r="B101" s="38" t="s">
+      <c r="B101" s="37" t="s">
         <v>99</v>
       </c>
       <c r="V101" s="6">
@@ -5351,42 +5525,42 @@
         <v>0</v>
       </c>
       <c r="W101" s="6">
-        <f t="shared" ref="W101:AE101" si="67">SUM(W97:W100)</f>
+        <f t="shared" ref="W101:AE101" si="68">SUM(W97:W100)</f>
         <v>0</v>
       </c>
       <c r="X101" s="6">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="Y101" s="6">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="Z101" s="6">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AA101" s="6">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AB101" s="6">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AC101" s="6">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AD101" s="6">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AE101" s="6">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
-      <c r="AG101" s="21" t="s">
+      <c r="AG101" s="20" t="s">
         <v>61</v>
       </c>
       <c r="AH101" s="9">
@@ -5395,7 +5569,7 @@
       </c>
     </row>
     <row r="102" spans="2:131" x14ac:dyDescent="0.2">
-      <c r="B102" s="38" t="s">
+      <c r="B102" s="37" t="s">
         <v>100</v>
       </c>
       <c r="AH102" s="14">
@@ -5404,7 +5578,7 @@
       </c>
     </row>
     <row r="103" spans="2:131" x14ac:dyDescent="0.2">
-      <c r="B103" s="38" t="s">
+      <c r="B103" s="37" t="s">
         <v>101</v>
       </c>
       <c r="V103" s="6">
@@ -5449,7 +5623,7 @@
       </c>
     </row>
     <row r="105" spans="2:131" x14ac:dyDescent="0.2">
-      <c r="B105" s="33" t="s">
+      <c r="B105" s="32" t="s">
         <v>26</v>
       </c>
       <c r="V105" s="6">
@@ -5473,23 +5647,23 @@
         <v>7285.1800613582691</v>
       </c>
       <c r="AA105" s="6">
-        <f t="shared" ref="AA105:AE105" si="68">AA88+AA91-AA89</f>
+        <f t="shared" ref="AA105:AE105" si="69">AA88+AA91-AA89</f>
         <v>8114.6257570889093</v>
       </c>
       <c r="AB105" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>8070.2879688436005</v>
       </c>
       <c r="AC105" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>9060.1628520994418</v>
       </c>
       <c r="AD105" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>10157.826808972313</v>
       </c>
       <c r="AE105" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>10005.057777890286</v>
       </c>
       <c r="AF105" s="6">
@@ -5821,21 +5995,243 @@
         <v>22624.148938042814</v>
       </c>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B121" s="38"/>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B122" s="38"/>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B123" s="38"/>
-    </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B124" s="38"/>
+    <row r="107" spans="2:131" x14ac:dyDescent="0.2">
+      <c r="B107" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="AG107" s="14">
+        <f>((NPV(AH99,Z105:DI105)+Main!K5-Main!K6)/Main!K3)/Main!K2-1</f>
+        <v>0.1215706396406917</v>
+      </c>
+      <c r="AH107" s="14">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AI107" s="14">
+        <v>0.08</v>
+      </c>
+      <c r="AJ107" s="15">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="AK107" s="14">
+        <v>0.09</v>
+      </c>
+      <c r="AL107" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="AM107" s="14">
+        <v>0.11</v>
+      </c>
+      <c r="AN107" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="108" spans="2:131" x14ac:dyDescent="0.2">
+      <c r="B108" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG108" s="6">
+        <v>40</v>
+      </c>
+      <c r="AH108" s="14">
+        <f t="dataTable" ref="AH108:AM114" dt2D="1" dtr="1" r1="AH99" r2="AA12"/>
+        <v>0.26097992479538878</v>
+      </c>
+      <c r="AI108" s="14">
+        <v>8.0123731707326229E-2</v>
+      </c>
+      <c r="AJ108" s="14">
+        <v>6.9663217485091966E-3</v>
+      </c>
+      <c r="AK108" s="14">
+        <v>-5.7321620680062968E-2</v>
+      </c>
+      <c r="AL108" s="14">
+        <v>-0.16487124560265543</v>
+      </c>
+      <c r="AM108" s="14">
+        <v>-0.25112361970896036</v>
+      </c>
+    </row>
+    <row r="109" spans="2:131" x14ac:dyDescent="0.2">
+      <c r="AG109" s="6">
+        <v>60</v>
+      </c>
+      <c r="AH109" s="14">
+        <v>0.31008316347590203</v>
+      </c>
+      <c r="AI109" s="14">
+        <v>0.12145911622895667</v>
+      </c>
+      <c r="AJ109" s="14">
+        <v>4.5167761045903365E-2</v>
+      </c>
+      <c r="AK109" s="14">
+        <v>-2.1869107240013341E-2</v>
+      </c>
+      <c r="AL109" s="14">
+        <v>-0.13400420915505484</v>
+      </c>
+      <c r="AM109" s="14">
+        <v>-0.22391846361753354</v>
+      </c>
+    </row>
+    <row r="110" spans="2:131" x14ac:dyDescent="0.2">
+      <c r="AG110" s="6">
+        <v>80</v>
+      </c>
+      <c r="AH110" s="14">
+        <v>0.35918640215641329</v>
+      </c>
+      <c r="AI110" s="14">
+        <v>0.16279450075058954</v>
+      </c>
+      <c r="AJ110" s="36">
+        <v>8.3369200343297978E-2</v>
+      </c>
+      <c r="AK110" s="14">
+        <v>1.3583406200036396E-2</v>
+      </c>
+      <c r="AL110" s="14">
+        <v>-0.10313717270745426</v>
+      </c>
+      <c r="AM110" s="14">
+        <v>-0.19671330752610672</v>
+      </c>
+    </row>
+    <row r="111" spans="2:131" x14ac:dyDescent="0.2">
+      <c r="AG111" s="6">
+        <v>100</v>
+      </c>
+      <c r="AH111" s="14">
+        <v>0.40828964083692565</v>
+      </c>
+      <c r="AI111" s="14">
+        <v>0.20412988527221931</v>
+      </c>
+      <c r="AJ111" s="12">
+        <v>0.1215706396406917</v>
+      </c>
+      <c r="AK111" s="14">
+        <v>4.9035919640084691E-2</v>
+      </c>
+      <c r="AL111" s="14">
+        <v>-7.2270136259853901E-2</v>
+      </c>
+      <c r="AM111" s="14">
+        <v>-0.16950815143468023</v>
+      </c>
+    </row>
+    <row r="112" spans="2:131" x14ac:dyDescent="0.2">
+      <c r="AG112" s="6">
+        <v>150</v>
+      </c>
+      <c r="AH112" s="14">
+        <v>0.53104773753820878</v>
+      </c>
+      <c r="AI112" s="14">
+        <v>0.30746834657629907</v>
+      </c>
+      <c r="AJ112" s="14">
+        <v>0.21707423788417923</v>
+      </c>
+      <c r="AK112" s="14">
+        <v>0.1376672032402102</v>
+      </c>
+      <c r="AL112" s="14">
+        <v>4.8974548591482758E-3</v>
+      </c>
+      <c r="AM112" s="14">
+        <v>-0.10149526120611319</v>
+      </c>
+    </row>
+    <row r="113" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="AG113" s="6">
+        <v>200</v>
+      </c>
+      <c r="AH113" s="14">
+        <v>0.65380583423948879</v>
+      </c>
+      <c r="AI113" s="14">
+        <v>0.41080680788037838</v>
+      </c>
+      <c r="AJ113" s="14">
+        <v>0.31257783612766388</v>
+      </c>
+      <c r="AK113" s="14">
+        <v>0.22629848684033482</v>
+      </c>
+      <c r="AL113" s="14">
+        <v>8.2065045978149342E-2</v>
+      </c>
+      <c r="AM113" s="14">
+        <v>-3.3482370977546139E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="AG114" s="6">
+        <v>300</v>
+      </c>
+      <c r="AH114" s="14">
+        <v>0.89932202764204972</v>
+      </c>
+      <c r="AI114" s="14">
+        <v>0.61748373048853611</v>
+      </c>
+      <c r="AJ114" s="14">
+        <v>0.50358503261463539</v>
+      </c>
+      <c r="AK114" s="14">
+        <v>0.40356105404058296</v>
+      </c>
+      <c r="AL114" s="14">
+        <v>0.23640022821615392</v>
+      </c>
+      <c r="AM114" s="14">
+        <v>0.10254340947958696</v>
+      </c>
+    </row>
+    <row r="115" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="AG115" s="32" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="116" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="AG116" s="32" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="121" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="B121" s="37"/>
+    </row>
+    <row r="122" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="B122" s="37"/>
+    </row>
+    <row r="123" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="B123" s="37"/>
+    </row>
+    <row r="124" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="B124" s="37"/>
+    </row>
+    <row r="127" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="AK127" s="32"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="AH108:AM114">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A1" location="Sheet1!A1" display="Main" xr:uid="{23B09628-C10F-428D-B1F6-3DB7F50BA868}"/>
+    <hyperlink ref="B107" location="Model!AG107" display="ARPU Sensitivity Analysis" xr:uid="{CD2E99ED-E0DD-431F-B56B-50C50F7E7545}"/>
+    <hyperlink ref="B108" location="Model!AG100" display="NPV" xr:uid="{93D05349-5F75-4F61-B38D-56A8C549A4AD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -5849,388 +6245,388 @@
   <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="34"/>
+    <col min="1" max="1" width="5" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>42</v>
       </c>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="34">
+      <c r="C2" s="33">
         <v>10638</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="38" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="33">
         <v>40</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="34" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="33">
         <v>15</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="32" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="33">
         <v>60</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="34" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="33">
         <f>(C2-(C4*12*C3))/((C5*12)-(C4*12))</f>
         <v>6.3666666666666663</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="32" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="33">
         <f>C3-C6</f>
         <v>33.633333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B8" s="8"/>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="33" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B9" s="8"/>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="33" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="33" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="39" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="33" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="33" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E15" s="34" t="s">
+      <c r="E15" s="33" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="33" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="33" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="20" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="E20" s="34" t="s">
+      <c r="E20" s="33" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="E21" s="34" t="s">
+      <c r="E21" s="33" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="E22" s="34" t="s">
+      <c r="E22" s="33" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="E23" s="34" t="s">
+      <c r="E23" s="33" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="E24" s="34" t="s">
+      <c r="E24" s="33" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="E26" s="39" t="s">
+      <c r="E26" s="38" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C28" s="34">
+      <c r="C28" s="33">
         <f>'CC Model'!C6*'CC Model'!C5*12</f>
         <v>4584</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="33">
         <v>5</v>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="33">
         <v>10</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="33">
         <v>15</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="33">
         <v>20</v>
       </c>
-      <c r="H28" s="34">
+      <c r="H28" s="33">
         <v>22</v>
       </c>
-      <c r="I28" s="34" t="s">
+      <c r="I28" s="33" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C29" s="34">
+      <c r="C29" s="33">
         <v>23</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="33">
         <f t="dataTable" ref="D29:H37" dt2D="1" dtr="1" r1="C4" r2="C5"/>
         <v>10526.333333333332</v>
       </c>
-      <c r="E29" s="34">
+      <c r="E29" s="33">
         <v>10328.76923076923</v>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="33">
         <v>9884.25</v>
       </c>
-      <c r="G29" s="34">
+      <c r="G29" s="33">
         <v>7958</v>
       </c>
-      <c r="H29" s="34">
+      <c r="H29" s="33">
         <v>1794</v>
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C30" s="34">
+      <c r="C30" s="33">
         <v>30</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="33">
         <v>9885.6</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="33">
         <v>8757</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="33">
         <v>6876</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="33">
         <v>3114</v>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="33">
         <v>292.5</v>
       </c>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C31" s="34">
+      <c r="C31" s="33">
         <v>40</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="33">
         <v>9414.8571428571431</v>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="33">
         <v>7784</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="33">
         <v>5500.8</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="33">
         <v>2076</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="33">
         <v>173.33333333333334</v>
       </c>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C32" s="34">
+      <c r="C32" s="33">
         <v>50</v>
       </c>
-      <c r="D32" s="34">
+      <c r="D32" s="33">
         <v>9153.3333333333339</v>
       </c>
-      <c r="E32" s="34">
+      <c r="E32" s="33">
         <v>7297.5</v>
       </c>
-      <c r="F32" s="34">
+      <c r="F32" s="33">
         <v>4911.4285714285716</v>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="33">
         <v>1730</v>
       </c>
-      <c r="H32" s="34">
+      <c r="H32" s="33">
         <v>139.28571428571428</v>
       </c>
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C33" s="34">
+      <c r="C33" s="33">
         <v>60</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="33">
         <v>8986.9090909090919</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="33">
         <v>7005.6</v>
       </c>
       <c r="F33" s="1">
         <v>4584</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="33">
         <v>1557</v>
       </c>
-      <c r="H33" s="34">
+      <c r="H33" s="33">
         <v>123.15789473684211</v>
       </c>
     </row>
     <row r="34" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C34" s="34">
+      <c r="C34" s="33">
         <v>70</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="33">
         <v>8871.6923076923067</v>
       </c>
-      <c r="E34" s="34">
+      <c r="E34" s="33">
         <v>6810.9999999999991</v>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="33">
         <v>4375.636363636364</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="33">
         <v>1453.1999999999998</v>
       </c>
-      <c r="H34" s="34">
+      <c r="H34" s="33">
         <v>113.75</v>
       </c>
     </row>
     <row r="35" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C35" s="34">
+      <c r="C35" s="33">
         <v>80</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="33">
         <v>8787.2000000000007</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="33">
         <v>6672</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="33">
         <v>4231.3846153846152</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="33">
         <v>1384</v>
       </c>
-      <c r="H35" s="34">
+      <c r="H35" s="33">
         <v>107.58620689655172</v>
       </c>
     </row>
     <row r="36" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C36" s="34">
+      <c r="C36" s="33">
         <v>90</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="33">
         <v>8722.5882352941171</v>
       </c>
-      <c r="E36" s="34">
+      <c r="E36" s="33">
         <v>6567.75</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="33">
         <v>4125.6000000000004</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="33">
         <v>1334.5714285714287</v>
       </c>
-      <c r="H36" s="34">
+      <c r="H36" s="33">
         <v>103.23529411764704</v>
       </c>
     </row>
     <row r="37" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C37" s="34">
+      <c r="C37" s="33">
         <v>100</v>
       </c>
-      <c r="D37" s="34">
+      <c r="D37" s="33">
         <v>8671.5789473684217</v>
       </c>
-      <c r="E37" s="34">
+      <c r="E37" s="33">
         <v>6486.6666666666661</v>
       </c>
-      <c r="F37" s="34">
+      <c r="F37" s="33">
         <v>4044.7058823529414</v>
       </c>
-      <c r="G37" s="34">
+      <c r="G37" s="33">
         <v>1297.5</v>
       </c>
-      <c r="H37" s="34">
+      <c r="H37" s="33">
         <v>99.999999999999986</v>
       </c>
     </row>
     <row r="38" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C38" s="34" t="s">
+      <c r="C38" s="33" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="39" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="E39" s="34" t="s">
+      <c r="E39" s="33" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="E40" s="34" t="s">
+      <c r="E40" s="33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="41" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="E41" s="33" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="41" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="E41" s="34" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -6262,31 +6658,37 @@
     <col min="2" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="40" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="20" t="s">
+      <c r="B1" s="33"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="33"/>
+      <c r="B2" s="40" t="s">
         <v>68</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
+    </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B4" s="34"/>
+      <c r="B4" s="33"/>
     </row>
     <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="35" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="33" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="33" t="s">
         <v>89</v>
       </c>
     </row>
@@ -6297,4 +6699,74 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B007B75-744E-4DFC-8BA9-D76EBC1DD8AE}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="33"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="40" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B3" s="33">
+        <v>2007</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B4" s="33">
+        <v>2012</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B5" s="33">
+        <v>2014</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B6" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B9" s="33">
+        <v>2024</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B10" s="33">
+        <v>2026</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{76F3B995-E50F-4483-9AB5-8E1385A731CD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>